--- a/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0">
+    <comment ref="D3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -55,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -83,14 +83,38 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
-  <si>
-    <t>#</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+  <si>
+    <t>##var</t>
   </si>
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>EffectType</t>
+  </si>
+  <si>
+    <t>EffectName</t>
+  </si>
+  <si>
+    <t>SkillEffectLiveTime</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
     <t>名称</t>
   </si>
   <si>
@@ -101,24 +125,6 @@
   </si>
   <si>
     <t>技能特效存在时间[毫秒]</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>EffectType</t>
-  </si>
-  <si>
-    <t>EffectName</t>
-  </si>
-  <si>
-    <t>SkillEffectLiveTime</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
   </si>
   <si>
     <t>战士普通攻击</t>
@@ -182,7 +188,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -351,13 +357,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -611,9 +610,7 @@
       <top style="thin">
         <color theme="0"/>
       </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -626,7 +623,9 @@
       <top style="thin">
         <color theme="0"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -876,9 +875,9 @@
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -887,9 +886,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1220,290 +1216,293 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:G18"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="2" width="10.875" style="2" customWidth="1"/>
-    <col min="3" max="5" width="17.875" style="2"/>
-    <col min="6" max="7" width="25.625" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="17.875" style="2"/>
+    <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
+    <col min="2" max="4" width="17.875" style="2"/>
+    <col min="5" max="6" width="25.625" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1"/>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="4:4">
-      <c r="D2" s="3" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C3" s="4" t="s">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="2:6">
+      <c r="B4" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="2:6">
+      <c r="B5" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="2:6">
+      <c r="B6" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="2:6">
+      <c r="B7" s="2">
+        <v>10000004</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="2:6">
+      <c r="B8" s="2">
+        <v>10000005</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="2">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="2:6">
+      <c r="B9" s="2">
+        <v>10000006</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="2:6">
+      <c r="B10" s="2">
+        <v>10000007</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="2">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="2:6">
+      <c r="B11" s="2">
+        <v>10000008</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="2:6">
+      <c r="B12" s="2">
+        <v>20000001</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="2">
         <v>2</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>5</v>
+      <c r="E12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1000</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>9</v>
+    <row r="13" customHeight="1" spans="2:6">
+      <c r="B13" s="2">
+        <v>20000002</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1000</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:7">
-      <c r="C5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>10</v>
+    <row r="14" customHeight="1" spans="2:6">
+      <c r="B14" s="2">
+        <v>20000003</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1000</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:7">
-      <c r="C6" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="2">
+    <row r="15" customHeight="1" spans="2:6">
+      <c r="B15" s="2">
+        <v>20000004</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="2">
         <v>1000</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:7">
-      <c r="C7" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2" t="s">
+    <row r="16" customHeight="1" spans="2:6">
+      <c r="B16" s="2">
+        <v>20000005</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:7">
-      <c r="C8" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:7">
-      <c r="C9" s="2">
-        <v>10000004</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="2">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:7">
-      <c r="C10" s="2">
-        <v>10000005</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="2">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="2">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:7">
-      <c r="C11" s="2">
-        <v>10000006</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="2">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:7">
-      <c r="C12" s="2">
-        <v>10000007</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="2">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:7">
-      <c r="C13" s="2">
-        <v>10000008</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="2">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:7">
-      <c r="C14" s="2">
-        <v>20000001</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="2">
-        <v>2</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:7">
-      <c r="C15" s="2">
-        <v>20000002</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="2">
-        <v>2</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:7">
-      <c r="C16" s="2">
-        <v>20000003</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="2">
-        <v>2</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:7">
-      <c r="C17" s="2">
-        <v>20000004</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="2">
-        <v>2</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:7">
-      <c r="C18" s="2">
-        <v>20000005</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="2">
-        <v>2</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="2">
+      <c r="F16" s="2">
         <v>3000</v>
       </c>
     </row>

--- a/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12795"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
+    <author>WPS</author>
   </authors>
   <commentList>
     <comment ref="D3" authorId="0">
@@ -78,12 +79,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="H3" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>WPS:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0固定位置 
+1挂在玩家身上 
+2跟随玩家</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -103,6 +128,15 @@
     <t>SkillEffectLiveTime</t>
   </si>
   <si>
+    <t>SkillEffectDelayTime</t>
+  </si>
+  <si>
+    <t>SkillParent</t>
+  </si>
+  <si>
+    <t>SkillParentPosition</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -112,6 +146,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -124,7 +161,16 @@
     <t>特效名称</t>
   </si>
   <si>
-    <t>技能特效存在时间[毫秒]</t>
+    <t>技能特效存在时间</t>
+  </si>
+  <si>
+    <t>技能特效延迟释放时间</t>
+  </si>
+  <si>
+    <t>绑定父级</t>
+  </si>
+  <si>
+    <t>绑定父级位置</t>
   </si>
   <si>
     <t>战士普通攻击</t>
@@ -360,12 +406,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1216,16 +1262,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="5"/>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
-    <col min="2" max="4" width="17.875" style="2"/>
-    <col min="5" max="6" width="25.625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="17.875" style="2"/>
+    <col min="2" max="3" width="17.875" style="2"/>
+    <col min="4" max="4" width="16.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.75" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1244,266 +1295,371 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:6">
+    <row r="4" customHeight="1" spans="2:8">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F4" s="2">
-        <v>1000</v>
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:6">
+    <row r="5" customHeight="1" spans="2:8">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>1000</v>
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:6">
+    <row r="6" customHeight="1" spans="2:8">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F6" s="2">
-        <v>1000</v>
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:6">
+    <row r="7" customHeight="1" spans="2:8">
       <c r="B7" s="2">
         <v>10000004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F7" s="2">
-        <v>2000</v>
+        <v>2</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:6">
+    <row r="8" customHeight="1" spans="2:8">
       <c r="B8" s="2">
         <v>10000005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F8" s="2">
-        <v>3000</v>
+        <v>3</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:6">
+    <row r="9" customHeight="1" spans="2:8">
       <c r="B9" s="2">
         <v>10000006</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F9" s="2">
-        <v>2000</v>
+        <v>2</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="2:6">
+    <row r="10" customHeight="1" spans="2:8">
       <c r="B10" s="2">
         <v>10000007</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F10" s="2">
-        <v>3000</v>
+        <v>3</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="2:6">
+    <row r="11" customHeight="1" spans="2:8">
       <c r="B11" s="2">
         <v>10000008</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F11" s="2">
-        <v>3000</v>
+        <v>3</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="2:6">
+    <row r="12" customHeight="1" spans="2:8">
       <c r="B12" s="2">
         <v>20000001</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2">
         <v>2</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F12" s="2">
-        <v>1000</v>
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="2:6">
+    <row r="13" customHeight="1" spans="2:8">
       <c r="B13" s="2">
         <v>20000002</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D13" s="2">
         <v>2</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F13" s="2">
-        <v>1000</v>
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="2:6">
+    <row r="14" customHeight="1" spans="2:8">
       <c r="B14" s="2">
         <v>20000003</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2">
         <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F14" s="2">
-        <v>1000</v>
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="2:6">
+    <row r="15" customHeight="1" spans="2:8">
       <c r="B15" s="2">
         <v>20000004</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D15" s="2">
         <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F15" s="2">
-        <v>1000</v>
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="2:6">
+    <row r="16" customHeight="1" spans="2:8">
       <c r="B16" s="2">
         <v>20000005</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F16" s="2">
-        <v>3000</v>
+        <v>3</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -216,6 +216,12 @@
   </si>
   <si>
     <t>受击特效</t>
+  </si>
+  <si>
+    <t>Eff_Test14</t>
+  </si>
+  <si>
+    <t>Center</t>
   </si>
   <si>
     <t>眩晕特效</t>
@@ -406,12 +412,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1547,7 +1553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="2:8">
+    <row r="12" customHeight="1" spans="2:9">
       <c r="B12" s="2">
         <v>20000001</v>
       </c>
@@ -1558,7 +1564,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F12" s="2">
         <v>1</v>
@@ -1567,10 +1573,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="2:8">
+    <row r="13" customHeight="1" spans="2:9">
       <c r="B13" s="2">
         <v>20000002</v>
       </c>
@@ -1581,7 +1590,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
@@ -1590,10 +1599,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="2:8">
+    <row r="14" customHeight="1" spans="2:9">
       <c r="B14" s="2">
         <v>20000003</v>
       </c>
@@ -1604,7 +1616,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F14" s="2">
         <v>1</v>
@@ -1613,15 +1625,18 @@
         <v>0</v>
       </c>
       <c r="H14" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="2:8">
+    <row r="15" customHeight="1" spans="2:9">
       <c r="B15" s="2">
         <v>20000004</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" s="2">
         <v>2</v>
@@ -1636,15 +1651,18 @@
         <v>0</v>
       </c>
       <c r="H15" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="2:8">
+    <row r="16" customHeight="1" spans="2:9">
       <c r="B16" s="2">
         <v>20000005</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -1659,7 +1677,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -1406,7 +1406,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -1429,7 +1429,7 @@
         <v>26</v>
       </c>
       <c r="F6" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>

--- a/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -176,40 +176,40 @@
     <t>战士普通攻击</t>
   </si>
   <si>
+    <t>箭手普通攻击</t>
+  </si>
+  <si>
+    <t>Eff_Test2</t>
+  </si>
+  <si>
+    <t>法师普通攻击</t>
+  </si>
+  <si>
+    <t>Eff_Test3</t>
+  </si>
+  <si>
+    <t>箭雨</t>
+  </si>
+  <si>
+    <t>Eff_Test4</t>
+  </si>
+  <si>
+    <t>治疗</t>
+  </si>
+  <si>
+    <t>Eff_Test5</t>
+  </si>
+  <si>
+    <t>岩石爆</t>
+  </si>
+  <si>
+    <t>Eff_Test6</t>
+  </si>
+  <si>
+    <t>通用持续性加血特效</t>
+  </si>
+  <si>
     <t>Eff_Test1</t>
-  </si>
-  <si>
-    <t>箭手普通攻击</t>
-  </si>
-  <si>
-    <t>Eff_Test2</t>
-  </si>
-  <si>
-    <t>法师普通攻击</t>
-  </si>
-  <si>
-    <t>Eff_Test3</t>
-  </si>
-  <si>
-    <t>箭雨</t>
-  </si>
-  <si>
-    <t>Eff_Test4</t>
-  </si>
-  <si>
-    <t>治疗</t>
-  </si>
-  <si>
-    <t>Eff_Test5</t>
-  </si>
-  <si>
-    <t>岩石爆</t>
-  </si>
-  <si>
-    <t>Eff_Test6</t>
-  </si>
-  <si>
-    <t>通用持续性加血特效</t>
   </si>
   <si>
     <t>通用瞬间加血特效</t>
@@ -412,12 +412,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1379,9 +1379,7 @@
       <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="E4" s="2"/>
       <c r="F4" s="2">
         <v>1</v>
       </c>
@@ -1397,13 +1395,13 @@
         <v>10000002</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
@@ -1420,13 +1418,13 @@
         <v>10000003</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="F6" s="2">
         <v>5</v>
@@ -1443,13 +1441,13 @@
         <v>10000004</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="F7" s="2">
         <v>2</v>
@@ -1466,13 +1464,13 @@
         <v>10000005</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="F8" s="2">
         <v>3</v>
@@ -1489,13 +1487,13 @@
         <v>10000006</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="F9" s="2">
         <v>2</v>
@@ -1512,13 +1510,13 @@
         <v>10000007</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F10" s="2">
         <v>3</v>
@@ -1541,7 +1539,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F11" s="2">
         <v>3</v>
@@ -1642,7 +1640,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -1668,7 +1666,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F16" s="2">
         <v>3</v>

--- a/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -412,12 +412,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1379,7 +1379,6 @@
       <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" s="2"/>
       <c r="F4" s="2">
         <v>1</v>
       </c>
@@ -1473,13 +1472,13 @@
         <v>29</v>
       </c>
       <c r="F8" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="2:8">

--- a/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -176,6 +176,9 @@
     <t>战士普通攻击</t>
   </si>
   <si>
+    <t>Center</t>
+  </si>
+  <si>
     <t>箭手普通攻击</t>
   </si>
   <si>
@@ -200,6 +203,9 @@
     <t>Eff_Test5</t>
   </si>
   <si>
+    <t>Bottom</t>
+  </si>
+  <si>
     <t>岩石爆</t>
   </si>
   <si>
@@ -219,9 +225,6 @@
   </si>
   <si>
     <t>Eff_Test14</t>
-  </si>
-  <si>
-    <t>Center</t>
   </si>
   <si>
     <t>眩晕特效</t>
@@ -1369,7 +1372,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:8">
+    <row r="4" customHeight="1" spans="2:9">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
@@ -1388,19 +1391,22 @@
       <c r="H4" s="2">
         <v>0</v>
       </c>
+      <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="5" customHeight="1" spans="2:8">
+    <row r="5" customHeight="1" spans="2:9">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
@@ -1411,19 +1417,22 @@
       <c r="H5" s="2">
         <v>0</v>
       </c>
+      <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="6" customHeight="1" spans="2:8">
+    <row r="6" customHeight="1" spans="2:9">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="2">
         <v>5</v>
@@ -1434,19 +1443,22 @@
       <c r="H6" s="2">
         <v>0</v>
       </c>
+      <c r="I6" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="7" customHeight="1" spans="2:8">
+    <row r="7" customHeight="1" spans="2:9">
       <c r="B7" s="2">
         <v>10000004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7" s="2">
         <v>2</v>
@@ -1457,19 +1469,22 @@
       <c r="H7" s="2">
         <v>0</v>
       </c>
+      <c r="I7" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="8" customHeight="1" spans="2:8">
+    <row r="8" customHeight="1" spans="2:9">
       <c r="B8" s="2">
         <v>10000005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8" s="2">
         <v>5</v>
@@ -1480,19 +1495,22 @@
       <c r="H8" s="2">
         <v>1</v>
       </c>
+      <c r="I8" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="9" customHeight="1" spans="2:8">
+    <row r="9" customHeight="1" spans="2:9">
       <c r="B9" s="2">
         <v>10000006</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F9" s="2">
         <v>2</v>
@@ -1503,19 +1521,22 @@
       <c r="H9" s="2">
         <v>0</v>
       </c>
+      <c r="I9" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="10" customHeight="1" spans="2:8">
+    <row r="10" customHeight="1" spans="2:9">
       <c r="B10" s="2">
         <v>10000007</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F10" s="2">
         <v>3</v>
@@ -1526,19 +1547,22 @@
       <c r="H10" s="2">
         <v>0</v>
       </c>
+      <c r="I10" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="11" customHeight="1" spans="2:8">
+    <row r="11" customHeight="1" spans="2:9">
       <c r="B11" s="2">
         <v>10000008</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F11" s="2">
         <v>3</v>
@@ -1548,6 +1572,9 @@
       </c>
       <c r="H11" s="2">
         <v>0</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="2:9">
@@ -1555,13 +1582,13 @@
         <v>20000001</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D12" s="2">
         <v>2</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F12" s="2">
         <v>1</v>
@@ -1573,7 +1600,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="2:9">
@@ -1581,13 +1608,13 @@
         <v>20000002</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D13" s="2">
         <v>2</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
@@ -1599,7 +1626,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="2:9">
@@ -1607,13 +1634,13 @@
         <v>20000003</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" s="2">
         <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F14" s="2">
         <v>1</v>
@@ -1625,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="2:9">
@@ -1633,13 +1660,13 @@
         <v>20000004</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" s="2">
         <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -1651,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="2:9">
@@ -1659,13 +1686,13 @@
         <v>20000005</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F16" s="2">
         <v>3</v>
@@ -1677,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -209,25 +209,25 @@
     <t>岩石爆</t>
   </si>
   <si>
+    <t>Eff_Test1</t>
+  </si>
+  <si>
+    <t>通用持续性加血特效</t>
+  </si>
+  <si>
+    <t>通用瞬间加血特效</t>
+  </si>
+  <si>
+    <t>受击特效</t>
+  </si>
+  <si>
+    <t>Eff_Test14</t>
+  </si>
+  <si>
+    <t>眩晕特效</t>
+  </si>
+  <si>
     <t>Eff_Test6</t>
-  </si>
-  <si>
-    <t>通用持续性加血特效</t>
-  </si>
-  <si>
-    <t>Eff_Test1</t>
-  </si>
-  <si>
-    <t>通用瞬间加血特效</t>
-  </si>
-  <si>
-    <t>受击特效</t>
-  </si>
-  <si>
-    <t>Eff_Test14</t>
-  </si>
-  <si>
-    <t>眩晕特效</t>
   </si>
   <si>
     <t>减速特效</t>
@@ -1536,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F10" s="2">
         <v>3</v>
@@ -1556,7 +1556,7 @@
         <v>10000008</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -1582,13 +1582,13 @@
         <v>20000001</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D12" s="2">
         <v>2</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F12" s="2">
         <v>1</v>
@@ -1608,13 +1608,13 @@
         <v>20000002</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" s="2">
         <v>2</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
@@ -1634,13 +1634,13 @@
         <v>20000003</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" s="2">
         <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F14" s="2">
         <v>1</v>
@@ -1660,13 +1660,13 @@
         <v>20000004</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" s="2">
         <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -1692,7 +1692,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F16" s="2">
         <v>3</v>

--- a/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="27945" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -176,9 +176,6 @@
     <t>战士普通攻击</t>
   </si>
   <si>
-    <t>Center</t>
-  </si>
-  <si>
     <t>箭手普通攻击</t>
   </si>
   <si>
@@ -194,7 +191,7 @@
     <t>箭雨</t>
   </si>
   <si>
-    <t>Eff_Test4</t>
+    <t>Eff_Test1</t>
   </si>
   <si>
     <t>治疗</t>
@@ -209,9 +206,6 @@
     <t>岩石爆</t>
   </si>
   <si>
-    <t>Eff_Test1</t>
-  </si>
-  <si>
     <t>通用持续性加血特效</t>
   </si>
   <si>
@@ -225,9 +219,6 @@
   </si>
   <si>
     <t>眩晕特效</t>
-  </si>
-  <si>
-    <t>Eff_Test6</t>
   </si>
   <si>
     <t>减速特效</t>
@@ -1372,7 +1363,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:9">
+    <row r="4" customHeight="1" spans="2:8">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
@@ -1391,22 +1382,19 @@
       <c r="H4" s="2">
         <v>0</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="5" customHeight="1" spans="2:9">
+    <row r="5" customHeight="1" spans="2:8">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
@@ -1417,22 +1405,19 @@
       <c r="H5" s="2">
         <v>0</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="6" customHeight="1" spans="2:9">
+    <row r="6" customHeight="1" spans="2:8">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="F6" s="2">
         <v>5</v>
@@ -1443,22 +1428,19 @@
       <c r="H6" s="2">
         <v>0</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="7" customHeight="1" spans="2:9">
+    <row r="7" customHeight="1" spans="2:8">
       <c r="B7" s="2">
         <v>10000004</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="F7" s="2">
         <v>2</v>
@@ -1468,9 +1450,6 @@
       </c>
       <c r="H7" s="2">
         <v>0</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="2:9">
@@ -1478,13 +1457,13 @@
         <v>10000005</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="F8" s="2">
         <v>5</v>
@@ -1496,21 +1475,21 @@
         <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:9">
+    <row r="9" customHeight="1" spans="2:8">
       <c r="B9" s="2">
         <v>10000006</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F9" s="2">
         <v>2</v>
@@ -1520,9 +1499,6 @@
       </c>
       <c r="H9" s="2">
         <v>0</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="2:9">
@@ -1530,13 +1506,13 @@
         <v>10000007</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F10" s="2">
         <v>3</v>
@@ -1545,10 +1521,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="2:9">
@@ -1556,13 +1532,13 @@
         <v>10000008</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F11" s="2">
         <v>3</v>
@@ -1571,24 +1547,24 @@
         <v>0</v>
       </c>
       <c r="H11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="2:9">
+    <row r="12" customHeight="1" spans="2:8">
       <c r="B12" s="2">
         <v>20000001</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D12" s="2">
         <v>2</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F12" s="2">
         <v>1</v>
@@ -1599,22 +1575,19 @@
       <c r="H12" s="2">
         <v>1</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="13" customHeight="1" spans="2:9">
+    <row r="13" customHeight="1" spans="2:8">
       <c r="B13" s="2">
         <v>20000002</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D13" s="2">
         <v>2</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
@@ -1625,22 +1598,19 @@
       <c r="H13" s="2">
         <v>1</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="14" customHeight="1" spans="2:9">
+    <row r="14" customHeight="1" spans="2:8">
       <c r="B14" s="2">
         <v>20000003</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D14" s="2">
         <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F14" s="2">
         <v>1</v>
@@ -1651,22 +1621,19 @@
       <c r="H14" s="2">
         <v>1</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="15" customHeight="1" spans="2:9">
+    <row r="15" customHeight="1" spans="2:8">
       <c r="B15" s="2">
         <v>20000004</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D15" s="2">
         <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -1677,22 +1644,19 @@
       <c r="H15" s="2">
         <v>1</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="16" customHeight="1" spans="2:9">
+    <row r="16" customHeight="1" spans="2:8">
       <c r="B16" s="2">
         <v>20000005</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F16" s="2">
         <v>3</v>
@@ -1702,9 +1666,6 @@
       </c>
       <c r="H16" s="2">
         <v>1</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>Eff_Test14</t>
+  </si>
+  <si>
+    <t>Center</t>
   </si>
   <si>
     <t>眩晕特效</t>
@@ -1553,7 +1556,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="2:8">
+    <row r="12" customHeight="1" spans="2:9">
       <c r="B12" s="2">
         <v>20000001</v>
       </c>
@@ -1575,8 +1578,11 @@
       <c r="H12" s="2">
         <v>1</v>
       </c>
+      <c r="I12" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="13" customHeight="1" spans="2:8">
+    <row r="13" customHeight="1" spans="2:9">
       <c r="B13" s="2">
         <v>20000002</v>
       </c>
@@ -1598,8 +1604,11 @@
       <c r="H13" s="2">
         <v>1</v>
       </c>
+      <c r="I13" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="14" customHeight="1" spans="2:8">
+    <row r="14" customHeight="1" spans="2:9">
       <c r="B14" s="2">
         <v>20000003</v>
       </c>
@@ -1621,13 +1630,16 @@
       <c r="H14" s="2">
         <v>1</v>
       </c>
+      <c r="I14" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="15" customHeight="1" spans="2:8">
+    <row r="15" customHeight="1" spans="2:9">
       <c r="B15" s="2">
         <v>20000004</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" s="2">
         <v>2</v>
@@ -1644,13 +1656,16 @@
       <c r="H15" s="2">
         <v>1</v>
       </c>
+      <c r="I15" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="16" customHeight="1" spans="2:8">
+    <row r="16" customHeight="1" spans="2:9">
       <c r="B16" s="2">
         <v>20000005</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -1666,6 +1681,9 @@
       </c>
       <c r="H16" s="2">
         <v>1</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>通用瞬间加血特效</t>
+  </si>
+  <si>
+    <t>燃烧</t>
   </si>
   <si>
     <t>受击特效</t>
@@ -1265,7 +1268,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
@@ -1558,19 +1561,19 @@
     </row>
     <row r="12" customHeight="1" spans="2:9">
       <c r="B12" s="2">
-        <v>20000001</v>
+        <v>10000009</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F12" s="2">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
@@ -1579,21 +1582,21 @@
         <v>1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="2:9">
       <c r="B13" s="2">
-        <v>20000002</v>
+        <v>20000001</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="2">
         <v>2</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
@@ -1605,21 +1608,21 @@
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="2:9">
       <c r="B14" s="2">
-        <v>20000003</v>
+        <v>20000002</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2">
         <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F14" s="2">
         <v>1</v>
@@ -1631,21 +1634,21 @@
         <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="2:9">
       <c r="B15" s="2">
-        <v>20000004</v>
+        <v>20000003</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D15" s="2">
         <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -1657,12 +1660,12 @@
         <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="2:9">
       <c r="B16" s="2">
-        <v>20000005</v>
+        <v>20000004</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>38</v>
@@ -1671,19 +1674,45 @@
         <v>2</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="2:9">
+      <c r="B17" s="2">
+        <v>20000005</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="2">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="2">
         <v>3</v>
       </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2">
-        <v>1</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>36</v>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -221,10 +221,10 @@
     <t>Eff_Test14</t>
   </si>
   <si>
+    <t>眩晕特效</t>
+  </si>
+  <si>
     <t>Center</t>
-  </si>
-  <si>
-    <t>眩晕特效</t>
   </si>
   <si>
     <t>减速特效</t>
@@ -1369,7 +1369,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:8">
+    <row r="4" customHeight="1" spans="1:9">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:8">
+    <row r="5" customHeight="1" spans="1:9">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:8">
+    <row r="6" customHeight="1" spans="1:9">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:8">
+    <row r="7" customHeight="1" spans="1:9">
       <c r="B7" s="2">
         <v>10000004</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:9">
+    <row r="8" customHeight="1" spans="1:9">
       <c r="B8" s="2">
         <v>10000005</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:8">
+    <row r="9" customHeight="1" spans="1:9">
       <c r="B9" s="2">
         <v>10000006</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="2:9">
+    <row r="10" customHeight="1" spans="1:9">
       <c r="B10" s="2">
         <v>10000007</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="2:9">
+    <row r="11" customHeight="1" spans="1:9">
       <c r="B11" s="2">
         <v>10000008</v>
       </c>
@@ -1559,7 +1559,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="2:9">
+    <row r="12" customHeight="1" spans="1:9">
       <c r="B12" s="2">
         <v>10000009</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="2:9">
+    <row r="13" customHeight="1" spans="1:9">
       <c r="B13" s="2">
         <v>20000001</v>
       </c>
@@ -1608,10 +1608,10 @@
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="2:9">
+    <row r="14" customHeight="1" spans="1:9">
       <c r="B14" s="2">
         <v>20000002</v>
       </c>
@@ -1634,10 +1634,10 @@
         <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="2:9">
+    <row r="15" customHeight="1" spans="1:9">
       <c r="B15" s="2">
         <v>20000003</v>
       </c>
@@ -1660,15 +1660,15 @@
         <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="2:9">
+    <row r="16" customHeight="1" spans="1:9">
       <c r="B16" s="2">
         <v>20000004</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -1686,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:9">
@@ -1712,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -176,6 +176,9 @@
     <t>战士普通攻击</t>
   </si>
   <si>
+    <t>Eff_Test1</t>
+  </si>
+  <si>
     <t>箭手普通攻击</t>
   </si>
   <si>
@@ -189,9 +192,6 @@
   </si>
   <si>
     <t>箭雨</t>
-  </si>
-  <si>
-    <t>Eff_Test1</t>
   </si>
   <si>
     <t>治疗</t>
@@ -1369,7 +1369,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:9">
+    <row r="4" customHeight="1" spans="2:8">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
@@ -1379,6 +1379,9 @@
       <c r="D4" s="2">
         <v>1</v>
       </c>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="F4" s="2">
         <v>1</v>
       </c>
@@ -1389,18 +1392,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:9">
+    <row r="5" customHeight="1" spans="2:8">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
@@ -1412,18 +1415,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:9">
+    <row r="6" customHeight="1" spans="2:8">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="2">
         <v>5</v>
@@ -1435,18 +1438,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:9">
+    <row r="7" customHeight="1" spans="2:8">
       <c r="B7" s="2">
         <v>10000004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F7" s="2">
         <v>2</v>
@@ -1458,7 +1461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:9">
+    <row r="8" customHeight="1" spans="2:9">
       <c r="B8" s="2">
         <v>10000005</v>
       </c>
@@ -1484,7 +1487,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:9">
+    <row r="9" customHeight="1" spans="2:8">
       <c r="B9" s="2">
         <v>10000006</v>
       </c>
@@ -1495,7 +1498,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F9" s="2">
         <v>2</v>
@@ -1507,7 +1510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:9">
+    <row r="10" customHeight="1" spans="2:9">
       <c r="B10" s="2">
         <v>10000007</v>
       </c>
@@ -1533,7 +1536,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:9">
+    <row r="11" customHeight="1" spans="2:9">
       <c r="B11" s="2">
         <v>10000008</v>
       </c>
@@ -1559,7 +1562,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:9">
+    <row r="12" customHeight="1" spans="2:9">
       <c r="B12" s="2">
         <v>10000009</v>
       </c>
@@ -1570,7 +1573,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F12" s="2">
         <v>9999</v>
@@ -1585,7 +1588,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:9">
+    <row r="13" customHeight="1" spans="2:9">
       <c r="B13" s="2">
         <v>20000001</v>
       </c>
@@ -1611,7 +1614,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:9">
+    <row r="14" customHeight="1" spans="2:9">
       <c r="B14" s="2">
         <v>20000002</v>
       </c>
@@ -1637,7 +1640,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:9">
+    <row r="15" customHeight="1" spans="2:9">
       <c r="B15" s="2">
         <v>20000003</v>
       </c>
@@ -1663,7 +1666,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:9">
+    <row r="16" customHeight="1" spans="2:9">
       <c r="B16" s="2">
         <v>20000004</v>
       </c>

--- a/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -176,34 +176,34 @@
     <t>战士普通攻击</t>
   </si>
   <si>
+    <t>Eff_Test2</t>
+  </si>
+  <si>
+    <t>箭手普通攻击</t>
+  </si>
+  <si>
+    <t>法师普通攻击</t>
+  </si>
+  <si>
+    <t>Eff_Test3</t>
+  </si>
+  <si>
+    <t>箭雨</t>
+  </si>
+  <si>
+    <t>治疗</t>
+  </si>
+  <si>
+    <t>Eff_Test5</t>
+  </si>
+  <si>
+    <t>Bottom</t>
+  </si>
+  <si>
+    <t>岩石爆</t>
+  </si>
+  <si>
     <t>Eff_Test1</t>
-  </si>
-  <si>
-    <t>箭手普通攻击</t>
-  </si>
-  <si>
-    <t>Eff_Test2</t>
-  </si>
-  <si>
-    <t>法师普通攻击</t>
-  </si>
-  <si>
-    <t>Eff_Test3</t>
-  </si>
-  <si>
-    <t>箭雨</t>
-  </si>
-  <si>
-    <t>治疗</t>
-  </si>
-  <si>
-    <t>Eff_Test5</t>
-  </si>
-  <si>
-    <t>Bottom</t>
-  </si>
-  <si>
-    <t>岩石爆</t>
   </si>
   <si>
     <t>通用持续性加血特效</t>
@@ -1369,7 +1369,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:8">
+    <row r="4" customHeight="1" spans="1:9">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:8">
+    <row r="5" customHeight="1" spans="1:9">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
@@ -1415,18 +1415,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:8">
+    <row r="6" customHeight="1" spans="1:9">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="F6" s="2">
         <v>5</v>
@@ -1438,12 +1438,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:8">
+    <row r="7" customHeight="1" spans="1:9">
       <c r="B7" s="2">
         <v>10000004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -1461,18 +1461,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="2:9">
+    <row r="8" customHeight="1" spans="1:9">
       <c r="B8" s="2">
         <v>10000005</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="F8" s="2">
         <v>5</v>
@@ -1484,21 +1484,21 @@
         <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:8">
+    <row r="9" customHeight="1" spans="1:9">
       <c r="B9" s="2">
         <v>10000006</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F9" s="2">
         <v>2</v>
@@ -1510,7 +1510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="2:9">
+    <row r="10" customHeight="1" spans="1:9">
       <c r="B10" s="2">
         <v>10000007</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10" s="2">
         <v>3</v>
@@ -1533,10 +1533,10 @@
         <v>1</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="2:9">
+    <row r="11" customHeight="1" spans="1:9">
       <c r="B11" s="2">
         <v>10000008</v>
       </c>
@@ -1547,7 +1547,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F11" s="2">
         <v>3</v>
@@ -1559,10 +1559,10 @@
         <v>1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="2:9">
+    <row r="12" customHeight="1" spans="1:9">
       <c r="B12" s="2">
         <v>10000009</v>
       </c>
@@ -1585,10 +1585,10 @@
         <v>1</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="2:9">
+    <row r="13" customHeight="1" spans="1:9">
       <c r="B13" s="2">
         <v>20000001</v>
       </c>
@@ -1611,10 +1611,10 @@
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="2:9">
+    <row r="14" customHeight="1" spans="1:9">
       <c r="B14" s="2">
         <v>20000002</v>
       </c>
@@ -1637,10 +1637,10 @@
         <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="2:9">
+    <row r="15" customHeight="1" spans="1:9">
       <c r="B15" s="2">
         <v>20000003</v>
       </c>
@@ -1663,10 +1663,10 @@
         <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="2:9">
+    <row r="16" customHeight="1" spans="1:9">
       <c r="B16" s="2">
         <v>20000004</v>
       </c>

--- a/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -221,10 +221,10 @@
     <t>Eff_Test14</t>
   </si>
   <si>
+    <t>Center</t>
+  </si>
+  <si>
     <t>眩晕特效</t>
-  </si>
-  <si>
-    <t>Center</t>
   </si>
   <si>
     <t>减速特效</t>
@@ -412,12 +412,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1611,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:9">
@@ -1637,7 +1637,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
@@ -1663,7 +1663,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:9">
@@ -1671,7 +1671,7 @@
         <v>20000004</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="2">
         <v>2</v>
@@ -1689,7 +1689,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:9">
@@ -1715,7 +1715,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/EffectConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EffectConfig.xlsx
@@ -412,12 +412,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1386,7 +1386,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>5</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="2">
         <v>0</v>
@@ -1432,7 +1432,7 @@
         <v>5</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="2">
         <v>0</v>
@@ -1455,7 +1455,7 @@
         <v>2</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
@@ -1478,7 +1478,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -1504,7 +1504,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
